--- a/preview/ci-artifacts/latest/project-plan-progress.xlsx
+++ b/preview/ci-artifacts/latest/project-plan-progress.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="177">
   <si>
     <t>workstream</t>
   </si>
@@ -488,6 +488,66 @@
   </si>
   <si>
     <t>latest_percent</t>
+  </si>
+  <si>
+    <t>Orientation-aware transforms and clipping implemented; synthetic fallback removed, placeholders gated by image evidence, image-object counting tightened to BIM/EIM, embedded image resolution now requires explicit AFPLib token overlap between BIM and BOC/EOC resources, draw-path prefers resource-resolved images before raw decode, selection policy runs through ImageResolutionService, and render-time resource selection is now strict per-image-index (no cross-index fallback bleed). Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Fallback narrowed substantially; low-signal run-level fallback retained only for guarded unresolved paths. Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Font/image/resource/print-centric trace diagnostics added; image binding diagnostics now include per-page BIM/candidate/overlap tokens plus candidate payload size and byte-prefix evidence, with explicit image render-path decisions (embedded/resource/raw/unresolved). Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Added operand-level PDF text operator traces, normalized PTX/alias histograms, cross-exam inference hints, and BIM/BOC/EOC timeline slices with inferred binding pairs. Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>2026-02-19T18:56:27Z</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>98,100</t>
+  </si>
+  <si>
+    <t>@@</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>90,100</t>
+  </si>
+  <si>
+    <t>%@</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>94,100</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>97,100</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>++</t>
+  </si>
+  <si>
+    <t>%%</t>
+  </si>
+  <si>
+    <t>--</t>
   </si>
 </sst>
 </file>
@@ -637,16 +697,16 @@
         <v>9</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>22</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6">
@@ -729,16 +789,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>35</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10">
@@ -867,16 +927,16 @@
         <v>38</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>51</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16">
@@ -1005,16 +1065,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>67</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22">
@@ -1346,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
@@ -2571,6 +2631,146 @@
       </c>
       <c r="K35" t="s" s="0">
         <v>99</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I36" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J36" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="K36" t="s" s="0">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E37" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G37" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H37" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="I37" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J37" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="K37" t="s" s="0">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E38" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F38" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="G38" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="H38" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="I38" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J38" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="K38" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="D39" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E39" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G39" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H39" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="I39" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J39" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="K39" t="s" s="0">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2579,7 +2779,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:dimension ref="A1:J35"/>
+  <ns0:dimension ref="A1:J39"/>
   <ns0:sheetData>
     <ns0:row r="1">
       <ns0:c r="A1" t="s" s="0">
@@ -3597,6 +3797,122 @@
       </ns0:c>
       <ns0:c r="I35" t="s" s="0">
         <ns0:v>117</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="36">
+      <ns0:c r="A36" t="s" s="0">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="B36" t="s" s="0">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="C36" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D36" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E36" t="s" s="0">
+        <ns0:v>83</ns0:v>
+      </ns0:c>
+      <ns0:c r="F36" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G36" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="H36" t="s" s="0">
+        <ns0:v>163</ns0:v>
+      </ns0:c>
+      <ns0:c r="I36" t="s" s="0">
+        <ns0:v>164</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="37">
+      <ns0:c r="A37" t="s" s="0">
+        <ns0:v>23</ns0:v>
+      </ns0:c>
+      <ns0:c r="B37" t="s" s="0">
+        <ns0:v>33</ns0:v>
+      </ns0:c>
+      <ns0:c r="C37" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D37" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E37" t="s" s="0">
+        <ns0:v>83</ns0:v>
+      </ns0:c>
+      <ns0:c r="F37" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G37" t="s" s="0">
+        <ns0:v>165</ns0:v>
+      </ns0:c>
+      <ns0:c r="H37" t="s" s="0">
+        <ns0:v>166</ns0:v>
+      </ns0:c>
+      <ns0:c r="I37" t="s" s="0">
+        <ns0:v>167</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="38">
+      <ns0:c r="A38" t="s" s="0">
+        <ns0:v>44</ns0:v>
+      </ns0:c>
+      <ns0:c r="B38" t="s" s="0">
+        <ns0:v>49</ns0:v>
+      </ns0:c>
+      <ns0:c r="C38" t="s" s="0">
+        <ns0:v>38</ns0:v>
+      </ns0:c>
+      <ns0:c r="D38" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E38" t="s" s="0">
+        <ns0:v>83</ns0:v>
+      </ns0:c>
+      <ns0:c r="F38" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G38" t="s" s="0">
+        <ns0:v>168</ns0:v>
+      </ns0:c>
+      <ns0:c r="H38" t="s" s="0">
+        <ns0:v>169</ns0:v>
+      </ns0:c>
+      <ns0:c r="I38" t="s" s="0">
+        <ns0:v>167</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="39">
+      <ns0:c r="A39" t="s" s="0">
+        <ns0:v>60</ns0:v>
+      </ns0:c>
+      <ns0:c r="B39" t="s" s="0">
+        <ns0:v>65</ns0:v>
+      </ns0:c>
+      <ns0:c r="C39" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D39" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E39" t="s" s="0">
+        <ns0:v>83</ns0:v>
+      </ns0:c>
+      <ns0:c r="F39" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G39" t="s" s="0">
+        <ns0:v>170</ns0:v>
+      </ns0:c>
+      <ns0:c r="H39" t="s" s="0">
+        <ns0:v>171</ns0:v>
+      </ns0:c>
+      <ns0:c r="I39" t="s" s="0">
+        <ns0:v>164</ns0:v>
       </ns0:c>
     </ns0:row>
   </ns0:sheetData>
@@ -3605,7 +3921,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:dimension ref="A1:AI39"/>
+  <ns0:dimension ref="A1:AI40"/>
   <ns0:sheetData>
     <ns0:row r="1">
       <ns0:c r="A1" t="s" s="0">
@@ -3821,45 +4137,141 @@
         <ns0:v>31</ns0:v>
       </ns0:c>
     </ns0:row>
-    <ns0:row r="5">
-      <ns0:c r="A5" t="s" s="0">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="B5" t="s" s="0">
-        <ns0:v>113</ns0:v>
-      </ns0:c>
-      <ns0:c r="C5" t="s" s="0">
-        <ns0:v>156</ns0:v>
+    <ns0:row r="3">
+      <ns0:c r="A3" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="G3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="H3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="I3" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="J3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="K3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="L3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="M3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="N3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="O3" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="P3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="Q3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="R3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="S3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="T3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="U3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="V3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="W3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="X3" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AB3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AC3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AD3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AI3" t="s" s="0">
+        <ns0:v>109</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="6">
       <ns0:c r="A6" t="s" s="0">
-        <ns0:v>122</ns0:v>
+        <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="B6" t="s" s="0">
-        <ns0:v>117</ns0:v>
+        <ns0:v>113</ns0:v>
       </ns0:c>
       <ns0:c r="C6" t="s" s="0">
-        <ns0:v>18</ns0:v>
+        <ns0:v>156</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="7">
       <ns0:c r="A7" t="s" s="0">
-        <ns0:v>123</ns0:v>
+        <ns0:v>122</ns0:v>
       </ns0:c>
       <ns0:c r="B7" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>172</ns0:v>
       </ns0:c>
       <ns0:c r="C7" t="s" s="0">
-        <ns0:v>21</ns0:v>
+        <ns0:v>18</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="8">
       <ns0:c r="A8" t="s" s="0">
-        <ns0:v>124</ns0:v>
+        <ns0:v>123</ns0:v>
       </ns0:c>
       <ns0:c r="B8" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C8" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -3867,10 +4279,10 @@
     </ns0:row>
     <ns0:row r="9">
       <ns0:c r="A9" t="s" s="0">
-        <ns0:v>125</ns0:v>
+        <ns0:v>124</ns0:v>
       </ns0:c>
       <ns0:c r="B9" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C9" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -3878,98 +4290,98 @@
     </ns0:row>
     <ns0:row r="10">
       <ns0:c r="A10" t="s" s="0">
-        <ns0:v>126</ns0:v>
+        <ns0:v>125</ns0:v>
       </ns0:c>
       <ns0:c r="B10" t="s" s="0">
-        <ns0:v>118</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C10" t="s" s="0">
-        <ns0:v>28</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="11">
       <ns0:c r="A11" t="s" s="0">
-        <ns0:v>127</ns0:v>
+        <ns0:v>126</ns0:v>
       </ns0:c>
       <ns0:c r="B11" t="s" s="0">
-        <ns0:v>118</ns0:v>
+        <ns0:v>173</ns0:v>
       </ns0:c>
       <ns0:c r="C11" t="s" s="0">
-        <ns0:v>25</ns0:v>
+        <ns0:v>28</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="12">
       <ns0:c r="A12" t="s" s="0">
-        <ns0:v>128</ns0:v>
+        <ns0:v>127</ns0:v>
       </ns0:c>
       <ns0:c r="B12" t="s" s="0">
-        <ns0:v>117</ns0:v>
+        <ns0:v>173</ns0:v>
       </ns0:c>
       <ns0:c r="C12" t="s" s="0">
-        <ns0:v>31</ns0:v>
+        <ns0:v>25</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="13">
       <ns0:c r="A13" t="s" s="0">
-        <ns0:v>129</ns0:v>
+        <ns0:v>128</ns0:v>
       </ns0:c>
       <ns0:c r="B13" t="s" s="0">
-        <ns0:v>119</ns0:v>
+        <ns0:v>172</ns0:v>
       </ns0:c>
       <ns0:c r="C13" t="s" s="0">
-        <ns0:v>34</ns0:v>
+        <ns0:v>31</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="14">
       <ns0:c r="A14" t="s" s="0">
-        <ns0:v>130</ns0:v>
+        <ns0:v>129</ns0:v>
       </ns0:c>
       <ns0:c r="B14" t="s" s="0">
-        <ns0:v>118</ns0:v>
+        <ns0:v>167</ns0:v>
       </ns0:c>
       <ns0:c r="C14" t="s" s="0">
-        <ns0:v>25</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="15">
       <ns0:c r="A15" t="s" s="0">
-        <ns0:v>131</ns0:v>
+        <ns0:v>130</ns0:v>
       </ns0:c>
       <ns0:c r="B15" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>173</ns0:v>
       </ns0:c>
       <ns0:c r="C15" t="s" s="0">
-        <ns0:v>11</ns0:v>
+        <ns0:v>25</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="16">
       <ns0:c r="A16" t="s" s="0">
-        <ns0:v>132</ns0:v>
+        <ns0:v>131</ns0:v>
       </ns0:c>
       <ns0:c r="B16" t="s" s="0">
-        <ns0:v>118</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C16" t="s" s="0">
-        <ns0:v>28</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="17">
       <ns0:c r="A17" t="s" s="0">
-        <ns0:v>133</ns0:v>
+        <ns0:v>132</ns0:v>
       </ns0:c>
       <ns0:c r="B17" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>173</ns0:v>
       </ns0:c>
       <ns0:c r="C17" t="s" s="0">
-        <ns0:v>11</ns0:v>
+        <ns0:v>28</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="18">
       <ns0:c r="A18" t="s" s="0">
-        <ns0:v>134</ns0:v>
+        <ns0:v>133</ns0:v>
       </ns0:c>
       <ns0:c r="B18" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C18" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -3977,21 +4389,21 @@
     </ns0:row>
     <ns0:row r="19">
       <ns0:c r="A19" t="s" s="0">
-        <ns0:v>135</ns0:v>
+        <ns0:v>134</ns0:v>
       </ns0:c>
       <ns0:c r="B19" t="s" s="0">
-        <ns0:v>119</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C19" t="s" s="0">
-        <ns0:v>50</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="20">
       <ns0:c r="A20" t="s" s="0">
-        <ns0:v>136</ns0:v>
+        <ns0:v>135</ns0:v>
       </ns0:c>
       <ns0:c r="B20" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>167</ns0:v>
       </ns0:c>
       <ns0:c r="C20" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -3999,10 +4411,10 @@
     </ns0:row>
     <ns0:row r="21">
       <ns0:c r="A21" t="s" s="0">
-        <ns0:v>137</ns0:v>
+        <ns0:v>136</ns0:v>
       </ns0:c>
       <ns0:c r="B21" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C21" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -4010,10 +4422,10 @@
     </ns0:row>
     <ns0:row r="22">
       <ns0:c r="A22" t="s" s="0">
-        <ns0:v>138</ns0:v>
+        <ns0:v>137</ns0:v>
       </ns0:c>
       <ns0:c r="B22" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C22" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -4021,32 +4433,32 @@
     </ns0:row>
     <ns0:row r="23">
       <ns0:c r="A23" t="s" s="0">
-        <ns0:v>139</ns0:v>
+        <ns0:v>138</ns0:v>
       </ns0:c>
       <ns0:c r="B23" t="s" s="0">
-        <ns0:v>120</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C23" t="s" s="0">
-        <ns0:v>54</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="24">
       <ns0:c r="A24" t="s" s="0">
-        <ns0:v>140</ns0:v>
+        <ns0:v>139</ns0:v>
       </ns0:c>
       <ns0:c r="B24" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>174</ns0:v>
       </ns0:c>
       <ns0:c r="C24" t="s" s="0">
-        <ns0:v>11</ns0:v>
+        <ns0:v>54</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="25">
       <ns0:c r="A25" t="s" s="0">
-        <ns0:v>141</ns0:v>
+        <ns0:v>140</ns0:v>
       </ns0:c>
       <ns0:c r="B25" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C25" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -4054,43 +4466,43 @@
     </ns0:row>
     <ns0:row r="26">
       <ns0:c r="A26" t="s" s="0">
-        <ns0:v>142</ns0:v>
+        <ns0:v>141</ns0:v>
       </ns0:c>
       <ns0:c r="B26" t="s" s="0">
-        <ns0:v>117</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C26" t="s" s="0">
-        <ns0:v>18</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="27">
       <ns0:c r="A27" t="s" s="0">
-        <ns0:v>143</ns0:v>
+        <ns0:v>142</ns0:v>
       </ns0:c>
       <ns0:c r="B27" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>172</ns0:v>
       </ns0:c>
       <ns0:c r="C27" t="s" s="0">
-        <ns0:v>11</ns0:v>
+        <ns0:v>18</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="28">
       <ns0:c r="A28" t="s" s="0">
-        <ns0:v>144</ns0:v>
+        <ns0:v>143</ns0:v>
       </ns0:c>
       <ns0:c r="B28" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C28" t="s" s="0">
-        <ns0:v>66</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="29">
       <ns0:c r="A29" t="s" s="0">
-        <ns0:v>145</ns0:v>
+        <ns0:v>144</ns0:v>
       </ns0:c>
       <ns0:c r="B29" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C29" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -4098,10 +4510,10 @@
     </ns0:row>
     <ns0:row r="30">
       <ns0:c r="A30" t="s" s="0">
-        <ns0:v>146</ns0:v>
+        <ns0:v>145</ns0:v>
       </ns0:c>
       <ns0:c r="B30" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C30" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -4109,76 +4521,76 @@
     </ns0:row>
     <ns0:row r="31">
       <ns0:c r="A31" t="s" s="0">
-        <ns0:v>147</ns0:v>
+        <ns0:v>146</ns0:v>
       </ns0:c>
       <ns0:c r="B31" t="s" s="0">
-        <ns0:v>119</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C31" t="s" s="0">
-        <ns0:v>69</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="32">
       <ns0:c r="A32" t="s" s="0">
-        <ns0:v>148</ns0:v>
+        <ns0:v>147</ns0:v>
       </ns0:c>
       <ns0:c r="B32" t="s" s="0">
-        <ns0:v>117</ns0:v>
+        <ns0:v>175</ns0:v>
       </ns0:c>
       <ns0:c r="C32" t="s" s="0">
-        <ns0:v>18</ns0:v>
+        <ns0:v>69</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="33">
       <ns0:c r="A33" t="s" s="0">
-        <ns0:v>149</ns0:v>
+        <ns0:v>148</ns0:v>
       </ns0:c>
       <ns0:c r="B33" t="s" s="0">
-        <ns0:v>120</ns0:v>
+        <ns0:v>172</ns0:v>
       </ns0:c>
       <ns0:c r="C33" t="s" s="0">
-        <ns0:v>54</ns0:v>
+        <ns0:v>18</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="34">
       <ns0:c r="A34" t="s" s="0">
-        <ns0:v>150</ns0:v>
+        <ns0:v>149</ns0:v>
       </ns0:c>
       <ns0:c r="B34" t="s" s="0">
-        <ns0:v>117</ns0:v>
+        <ns0:v>174</ns0:v>
       </ns0:c>
       <ns0:c r="C34" t="s" s="0">
-        <ns0:v>31</ns0:v>
+        <ns0:v>54</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="35">
       <ns0:c r="A35" t="s" s="0">
-        <ns0:v>151</ns0:v>
+        <ns0:v>150</ns0:v>
       </ns0:c>
       <ns0:c r="B35" t="s" s="0">
-        <ns0:v>121</ns0:v>
+        <ns0:v>172</ns0:v>
       </ns0:c>
       <ns0:c r="C35" t="s" s="0">
-        <ns0:v>90</ns0:v>
+        <ns0:v>31</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="36">
       <ns0:c r="A36" t="s" s="0">
-        <ns0:v>152</ns0:v>
+        <ns0:v>151</ns0:v>
       </ns0:c>
       <ns0:c r="B36" t="s" s="0">
-        <ns0:v>117</ns0:v>
+        <ns0:v>176</ns0:v>
       </ns0:c>
       <ns0:c r="C36" t="s" s="0">
-        <ns0:v>18</ns0:v>
+        <ns0:v>90</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="37">
       <ns0:c r="A37" t="s" s="0">
-        <ns0:v>153</ns0:v>
+        <ns0:v>152</ns0:v>
       </ns0:c>
       <ns0:c r="B37" t="s" s="0">
-        <ns0:v>117</ns0:v>
+        <ns0:v>172</ns0:v>
       </ns0:c>
       <ns0:c r="C37" t="s" s="0">
         <ns0:v>18</ns0:v>
@@ -4186,23 +4598,34 @@
     </ns0:row>
     <ns0:row r="38">
       <ns0:c r="A38" t="s" s="0">
-        <ns0:v>154</ns0:v>
+        <ns0:v>153</ns0:v>
       </ns0:c>
       <ns0:c r="B38" t="s" s="0">
-        <ns0:v>118</ns0:v>
+        <ns0:v>172</ns0:v>
       </ns0:c>
       <ns0:c r="C38" t="s" s="0">
-        <ns0:v>25</ns0:v>
+        <ns0:v>18</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="39">
       <ns0:c r="A39" t="s" s="0">
+        <ns0:v>154</ns0:v>
+      </ns0:c>
+      <ns0:c r="B39" t="s" s="0">
+        <ns0:v>173</ns0:v>
+      </ns0:c>
+      <ns0:c r="C39" t="s" s="0">
+        <ns0:v>25</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="40">
+      <ns0:c r="A40" t="s" s="0">
         <ns0:v>155</ns0:v>
       </ns0:c>
-      <ns0:c r="B39" t="s" s="0">
-        <ns0:v>117</ns0:v>
-      </ns0:c>
-      <ns0:c r="C39" t="s" s="0">
+      <ns0:c r="B40" t="s" s="0">
+        <ns0:v>172</ns0:v>
+      </ns0:c>
+      <ns0:c r="C40" t="s" s="0">
         <ns0:v>31</ns0:v>
       </ns0:c>
     </ns0:row>

--- a/preview/ci-artifacts/latest/project-plan-progress.xlsx
+++ b/preview/ci-artifacts/latest/project-plan-progress.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2801" uniqueCount="177">
   <si>
     <t>workstream</t>
   </si>

--- a/preview/ci-artifacts/latest/project-plan-progress.xlsx
+++ b/preview/ci-artifacts/latest/project-plan-progress.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2801" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3619" uniqueCount="177">
   <si>
     <t>workstream</t>
   </si>

--- a/preview/ci-artifacts/latest/project-plan-progress.xlsx
+++ b/preview/ci-artifacts/latest/project-plan-progress.xlsx
@@ -11,13 +11,13 @@
     <ns0:sheet name="Progress Graph" sheetId="4" ns1:id="rId4"/>
   </ns0:sheets>
   <ns0:definedNames>
-    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Current Progress'!$A$1:$G$35</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Current Progress'!$A$1:$G$38</ns0:definedName>
   </ns0:definedNames>
 </ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3619" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5760" uniqueCount="223">
   <si>
     <t>workstream</t>
   </si>
@@ -548,6 +548,144 @@
   </si>
   <si>
     <t>--</t>
+  </si>
+  <si>
+    <t>Workstream H</t>
+  </si>
+  <si>
+    <t>migrate folders to canonical policy/management/product structure</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>Workspace reorganized to canonical realm layout with compatibility handling.</t>
+  </si>
+  <si>
+    <t>normalize manifests/security config and realm SQL tokens to canonical names</t>
+  </si>
+  <si>
+    <t>Realm naming and path references updated for policy/management/product semantics.</t>
+  </si>
+  <si>
+    <t>update gates/tests/report paths and validate full quality gate on migrated structure</t>
+  </si>
+  <si>
+    <t>Quality gate validation completed after migration fixes for artifact indexing, tooling guards, tests, and fidelity gate pathing.</t>
+  </si>
+  <si>
+    <t>2026-02-20T02:19:29Z</t>
+  </si>
+  <si>
+    <t>Workstream H | migrate folders to canonical policy/management/product structure</t>
+  </si>
+  <si>
+    <t>Workstream H | normalize manifests/security config and realm SQL tokens to canonical names</t>
+  </si>
+  <si>
+    <t>Workstream H | update gates/tests/report paths and validate full quality gate on migrated structure</t>
+  </si>
+  <si>
+    <t>Core line/box primitives implemented; additional AFP graphics semantics still pending. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Scoped CFI resolution implemented; sample path gaps remain due missing SCFL/CFI visibility. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Mixed run decode and mapping diagnostics implemented; further parity tuning required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Initial metric/spacing tuning added; still significant visual drift vs IBM sample. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Common signature-based and raw fallback paths available; coverage not exhaustive. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Per-format tests added and image-heavy sample included; corpus expansion remains. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Current corpus has limited coverage and needs broader document diversity. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Strong test base exists; additional parity-focused regression slices still required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Extended PTX alias normalization and image evidence diagnostics, filtered non-raster BIM payloads, switched to deterministic matching, surfaced token+payload binding evidence (sample shows JPEG candidate payload with zero BIM token overlap), implemented evidence-driven resource-first image selection with dedicated image-resolution policy service, and added confidence-aware embedded-resource matching (token/sequence/size heuristics) with strict per-object fallback behavior. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added SQL schema and upsert/link commands for decision_log and decision_dependency in realm DBs. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added export command and Gradle decisionPriorityReport task for pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Workflow and manifest wiring in progress to make decision state a first-class execution driver. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Pending initial population of decision records for renderer and boilerplate promotion actions. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added project-state knowledge tables and commands for entries/evidence/decision links. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added knowledgeBaseReport task and workflow wiring; now needs broader seeding coverage. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added intent-style report command, screen payload format, DB allowlist auth, and granular refresh options. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added reasoning sync pipeline, dual reasoning DBs, and reasoning-drive report with workflow integration. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>2026-02-23T17:34:22Z</t>
+  </si>
+  <si>
+    <t>70,100</t>
+  </si>
+  <si>
+    <t>*@</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>75,100</t>
+  </si>
+  <si>
+    <t>#@</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>80,100</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>65,100</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>60,100</t>
+  </si>
+  <si>
+    <t>+@</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>93,100</t>
+  </si>
+  <si>
+    <t>30,100</t>
+  </si>
+  <si>
+    <t>-@</t>
   </si>
 </sst>
 </file>
@@ -592,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G38"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
@@ -674,16 +812,16 @@
         <v>9</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>19</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5">
@@ -720,16 +858,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>26</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
@@ -743,16 +881,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>29</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8">
@@ -766,16 +904,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>32</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9">
@@ -812,16 +950,16 @@
         <v>38</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>39</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
@@ -858,16 +996,16 @@
         <v>38</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>43</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -950,16 +1088,16 @@
         <v>38</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>55</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17">
@@ -973,16 +1111,16 @@
         <v>38</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>57</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18">
@@ -1088,16 +1226,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>70</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23">
@@ -1226,16 +1364,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E28" t="s" s="0">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F28" t="s" s="0">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>84</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29">
@@ -1249,16 +1387,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E29" t="s" s="0">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F29" t="s" s="0">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>86</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30">
@@ -1272,16 +1410,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E30" t="s" s="0">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>88</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31">
@@ -1295,16 +1433,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E31" t="s" s="0">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="F31" t="s" s="0">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>91</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32">
@@ -1318,16 +1456,16 @@
         <v>9</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E32" t="s" s="0">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F32" t="s" s="0">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>93</v>
+        <v>202</v>
       </c>
     </row>
     <row r="33">
@@ -1341,16 +1479,16 @@
         <v>9</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E33" t="s" s="0">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>95</v>
+        <v>203</v>
       </c>
     </row>
     <row r="34">
@@ -1364,16 +1502,16 @@
         <v>9</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E34" t="s" s="0">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>97</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35">
@@ -1387,26 +1525,95 @@
         <v>9</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E35" t="s" s="0">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F35" t="s" s="0">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="G35" t="s" s="0">
-        <v>99</v>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E37" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F37" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="G37" t="s" s="0">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E38" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F38" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="G38" t="s" s="0">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G35"/>
+  <autoFilter ref="A1:G38"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K59"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
@@ -2771,6 +2978,706 @@
       </c>
       <c r="K39" t="s" s="0">
         <v>160</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="D40" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="E40" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F40" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="G40" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H40" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="I40" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J40" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K40" t="s" s="0">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="D41" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="E41" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="G41" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H41" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="I41" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J41" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K41" t="s" s="0">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="D42" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="E42" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F42" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="G42" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H42" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="I42" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J42" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K42" t="s" s="0">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D43" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E43" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F43" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G43" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H43" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="I43" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J43" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K43" t="s" s="0">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D44" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E44" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F44" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G44" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H44" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="I44" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J44" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K44" t="s" s="0">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D45" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E45" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F45" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G45" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H45" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="I45" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J45" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K45" t="s" s="0">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D46" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E46" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F46" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G46" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H46" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="I46" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J46" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K46" t="s" s="0">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="D47" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E47" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F47" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="G47" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="H47" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="I47" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J47" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K47" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D48" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E48" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F48" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="G48" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="H48" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="I48" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J48" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K48" t="s" s="0">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="D49" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E49" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F49" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="G49" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="H49" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="I49" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J49" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K49" t="s" s="0">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="D50" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E50" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F50" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="G50" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="H50" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="I50" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J50" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K50" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D51" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E51" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F51" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G51" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H51" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="I51" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J51" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K51" t="s" s="0">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="D52" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E52" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F52" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G52" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H52" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="I52" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J52" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K52" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="D53" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E53" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F53" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G53" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H53" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="I53" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J53" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K53" t="s" s="0">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="D54" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E54" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F54" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G54" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H54" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="I54" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J54" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K54" t="s" s="0">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="D55" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E55" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F55" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G55" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H55" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="I55" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J55" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K55" t="s" s="0">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="D56" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E56" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F56" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G56" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H56" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="I56" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J56" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K56" t="s" s="0">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="D57" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E57" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F57" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G57" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H57" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="I57" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J57" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K57" t="s" s="0">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="D58" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E58" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F58" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G58" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H58" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="I58" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J58" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K58" t="s" s="0">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="D59" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E59" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F59" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G59" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H59" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="I59" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J59" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="K59" t="s" s="0">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -2779,7 +3686,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:dimension ref="A1:J39"/>
+  <ns0:dimension ref="A1:J59"/>
   <ns0:sheetData>
     <ns0:row r="1">
       <ns0:c r="A1" t="s" s="0">
@@ -3913,6 +4820,586 @@
       </ns0:c>
       <ns0:c r="I39" t="s" s="0">
         <ns0:v>164</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="40">
+      <ns0:c r="A40" t="s" s="0">
+        <ns0:v>177</ns0:v>
+      </ns0:c>
+      <ns0:c r="B40" t="s" s="0">
+        <ns0:v>178</ns0:v>
+      </ns0:c>
+      <ns0:c r="C40" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D40" t="s" s="0">
+        <ns0:v>115</ns0:v>
+      </ns0:c>
+      <ns0:c r="E40" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F40" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G40" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="H40" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="I40" t="s" s="0">
+        <ns0:v>116</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="41">
+      <ns0:c r="A41" t="s" s="0">
+        <ns0:v>177</ns0:v>
+      </ns0:c>
+      <ns0:c r="B41" t="s" s="0">
+        <ns0:v>181</ns0:v>
+      </ns0:c>
+      <ns0:c r="C41" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D41" t="s" s="0">
+        <ns0:v>115</ns0:v>
+      </ns0:c>
+      <ns0:c r="E41" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F41" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G41" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="H41" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="I41" t="s" s="0">
+        <ns0:v>116</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="42">
+      <ns0:c r="A42" t="s" s="0">
+        <ns0:v>177</ns0:v>
+      </ns0:c>
+      <ns0:c r="B42" t="s" s="0">
+        <ns0:v>183</ns0:v>
+      </ns0:c>
+      <ns0:c r="C42" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D42" t="s" s="0">
+        <ns0:v>115</ns0:v>
+      </ns0:c>
+      <ns0:c r="E42" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F42" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G42" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="H42" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="I42" t="s" s="0">
+        <ns0:v>116</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="43">
+      <ns0:c r="A43" t="s" s="0">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="B43" t="s" s="0">
+        <ns0:v>16</ns0:v>
+      </ns0:c>
+      <ns0:c r="C43" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D43" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E43" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F43" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G43" t="s" s="0">
+        <ns0:v>90</ns0:v>
+      </ns0:c>
+      <ns0:c r="H43" t="s" s="0">
+        <ns0:v>207</ns0:v>
+      </ns0:c>
+      <ns0:c r="I43" t="s" s="0">
+        <ns0:v>208</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="44">
+      <ns0:c r="A44" t="s" s="0">
+        <ns0:v>23</ns0:v>
+      </ns0:c>
+      <ns0:c r="B44" t="s" s="0">
+        <ns0:v>24</ns0:v>
+      </ns0:c>
+      <ns0:c r="C44" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D44" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E44" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F44" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G44" t="s" s="0">
+        <ns0:v>209</ns0:v>
+      </ns0:c>
+      <ns0:c r="H44" t="s" s="0">
+        <ns0:v>210</ns0:v>
+      </ns0:c>
+      <ns0:c r="I44" t="s" s="0">
+        <ns0:v>211</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="45">
+      <ns0:c r="A45" t="s" s="0">
+        <ns0:v>23</ns0:v>
+      </ns0:c>
+      <ns0:c r="B45" t="s" s="0">
+        <ns0:v>27</ns0:v>
+      </ns0:c>
+      <ns0:c r="C45" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D45" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E45" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F45" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G45" t="s" s="0">
+        <ns0:v>212</ns0:v>
+      </ns0:c>
+      <ns0:c r="H45" t="s" s="0">
+        <ns0:v>213</ns0:v>
+      </ns0:c>
+      <ns0:c r="I45" t="s" s="0">
+        <ns0:v>211</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="46">
+      <ns0:c r="A46" t="s" s="0">
+        <ns0:v>23</ns0:v>
+      </ns0:c>
+      <ns0:c r="B46" t="s" s="0">
+        <ns0:v>30</ns0:v>
+      </ns0:c>
+      <ns0:c r="C46" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D46" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E46" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F46" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G46" t="s" s="0">
+        <ns0:v>214</ns0:v>
+      </ns0:c>
+      <ns0:c r="H46" t="s" s="0">
+        <ns0:v>215</ns0:v>
+      </ns0:c>
+      <ns0:c r="I46" t="s" s="0">
+        <ns0:v>208</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="47">
+      <ns0:c r="A47" t="s" s="0">
+        <ns0:v>36</ns0:v>
+      </ns0:c>
+      <ns0:c r="B47" t="s" s="0">
+        <ns0:v>37</ns0:v>
+      </ns0:c>
+      <ns0:c r="C47" t="s" s="0">
+        <ns0:v>38</ns0:v>
+      </ns0:c>
+      <ns0:c r="D47" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E47" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F47" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G47" t="s" s="0">
+        <ns0:v>212</ns0:v>
+      </ns0:c>
+      <ns0:c r="H47" t="s" s="0">
+        <ns0:v>213</ns0:v>
+      </ns0:c>
+      <ns0:c r="I47" t="s" s="0">
+        <ns0:v>211</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="48">
+      <ns0:c r="A48" t="s" s="0">
+        <ns0:v>36</ns0:v>
+      </ns0:c>
+      <ns0:c r="B48" t="s" s="0">
+        <ns0:v>42</ns0:v>
+      </ns0:c>
+      <ns0:c r="C48" t="s" s="0">
+        <ns0:v>38</ns0:v>
+      </ns0:c>
+      <ns0:c r="D48" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E48" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F48" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G48" t="s" s="0">
+        <ns0:v>209</ns0:v>
+      </ns0:c>
+      <ns0:c r="H48" t="s" s="0">
+        <ns0:v>210</ns0:v>
+      </ns0:c>
+      <ns0:c r="I48" t="s" s="0">
+        <ns0:v>211</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="49">
+      <ns0:c r="A49" t="s" s="0">
+        <ns0:v>52</ns0:v>
+      </ns0:c>
+      <ns0:c r="B49" t="s" s="0">
+        <ns0:v>53</ns0:v>
+      </ns0:c>
+      <ns0:c r="C49" t="s" s="0">
+        <ns0:v>38</ns0:v>
+      </ns0:c>
+      <ns0:c r="D49" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E49" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F49" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G49" t="s" s="0">
+        <ns0:v>216</ns0:v>
+      </ns0:c>
+      <ns0:c r="H49" t="s" s="0">
+        <ns0:v>217</ns0:v>
+      </ns0:c>
+      <ns0:c r="I49" t="s" s="0">
+        <ns0:v>218</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="50">
+      <ns0:c r="A50" t="s" s="0">
+        <ns0:v>52</ns0:v>
+      </ns0:c>
+      <ns0:c r="B50" t="s" s="0">
+        <ns0:v>56</ns0:v>
+      </ns0:c>
+      <ns0:c r="C50" t="s" s="0">
+        <ns0:v>38</ns0:v>
+      </ns0:c>
+      <ns0:c r="D50" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E50" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F50" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G50" t="s" s="0">
+        <ns0:v>90</ns0:v>
+      </ns0:c>
+      <ns0:c r="H50" t="s" s="0">
+        <ns0:v>207</ns0:v>
+      </ns0:c>
+      <ns0:c r="I50" t="s" s="0">
+        <ns0:v>208</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="51">
+      <ns0:c r="A51" t="s" s="0">
+        <ns0:v>60</ns0:v>
+      </ns0:c>
+      <ns0:c r="B51" t="s" s="0">
+        <ns0:v>68</ns0:v>
+      </ns0:c>
+      <ns0:c r="C51" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D51" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E51" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F51" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G51" t="s" s="0">
+        <ns0:v>219</ns0:v>
+      </ns0:c>
+      <ns0:c r="H51" t="s" s="0">
+        <ns0:v>220</ns0:v>
+      </ns0:c>
+      <ns0:c r="I51" t="s" s="0">
+        <ns0:v>167</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="52">
+      <ns0:c r="A52" t="s" s="0">
+        <ns0:v>81</ns0:v>
+      </ns0:c>
+      <ns0:c r="B52" t="s" s="0">
+        <ns0:v>82</ns0:v>
+      </ns0:c>
+      <ns0:c r="C52" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D52" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E52" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F52" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G52" t="s" s="0">
+        <ns0:v>209</ns0:v>
+      </ns0:c>
+      <ns0:c r="H52" t="s" s="0">
+        <ns0:v>210</ns0:v>
+      </ns0:c>
+      <ns0:c r="I52" t="s" s="0">
+        <ns0:v>211</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="53">
+      <ns0:c r="A53" t="s" s="0">
+        <ns0:v>81</ns0:v>
+      </ns0:c>
+      <ns0:c r="B53" t="s" s="0">
+        <ns0:v>85</ns0:v>
+      </ns0:c>
+      <ns0:c r="C53" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D53" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E53" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F53" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G53" t="s" s="0">
+        <ns0:v>90</ns0:v>
+      </ns0:c>
+      <ns0:c r="H53" t="s" s="0">
+        <ns0:v>207</ns0:v>
+      </ns0:c>
+      <ns0:c r="I53" t="s" s="0">
+        <ns0:v>208</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="54">
+      <ns0:c r="A54" t="s" s="0">
+        <ns0:v>81</ns0:v>
+      </ns0:c>
+      <ns0:c r="B54" t="s" s="0">
+        <ns0:v>87</ns0:v>
+      </ns0:c>
+      <ns0:c r="C54" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D54" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E54" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F54" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G54" t="s" s="0">
+        <ns0:v>214</ns0:v>
+      </ns0:c>
+      <ns0:c r="H54" t="s" s="0">
+        <ns0:v>215</ns0:v>
+      </ns0:c>
+      <ns0:c r="I54" t="s" s="0">
+        <ns0:v>208</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="55">
+      <ns0:c r="A55" t="s" s="0">
+        <ns0:v>81</ns0:v>
+      </ns0:c>
+      <ns0:c r="B55" t="s" s="0">
+        <ns0:v>89</ns0:v>
+      </ns0:c>
+      <ns0:c r="C55" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D55" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E55" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F55" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G55" t="s" s="0">
+        <ns0:v>18</ns0:v>
+      </ns0:c>
+      <ns0:c r="H55" t="s" s="0">
+        <ns0:v>221</ns0:v>
+      </ns0:c>
+      <ns0:c r="I55" t="s" s="0">
+        <ns0:v>222</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="56">
+      <ns0:c r="A56" t="s" s="0">
+        <ns0:v>81</ns0:v>
+      </ns0:c>
+      <ns0:c r="B56" t="s" s="0">
+        <ns0:v>92</ns0:v>
+      </ns0:c>
+      <ns0:c r="C56" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D56" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E56" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F56" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G56" t="s" s="0">
+        <ns0:v>90</ns0:v>
+      </ns0:c>
+      <ns0:c r="H56" t="s" s="0">
+        <ns0:v>207</ns0:v>
+      </ns0:c>
+      <ns0:c r="I56" t="s" s="0">
+        <ns0:v>208</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="57">
+      <ns0:c r="A57" t="s" s="0">
+        <ns0:v>81</ns0:v>
+      </ns0:c>
+      <ns0:c r="B57" t="s" s="0">
+        <ns0:v>94</ns0:v>
+      </ns0:c>
+      <ns0:c r="C57" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D57" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E57" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F57" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G57" t="s" s="0">
+        <ns0:v>216</ns0:v>
+      </ns0:c>
+      <ns0:c r="H57" t="s" s="0">
+        <ns0:v>217</ns0:v>
+      </ns0:c>
+      <ns0:c r="I57" t="s" s="0">
+        <ns0:v>218</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="58">
+      <ns0:c r="A58" t="s" s="0">
+        <ns0:v>81</ns0:v>
+      </ns0:c>
+      <ns0:c r="B58" t="s" s="0">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="C58" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D58" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E58" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F58" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G58" t="s" s="0">
+        <ns0:v>214</ns0:v>
+      </ns0:c>
+      <ns0:c r="H58" t="s" s="0">
+        <ns0:v>215</ns0:v>
+      </ns0:c>
+      <ns0:c r="I58" t="s" s="0">
+        <ns0:v>208</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="59">
+      <ns0:c r="A59" t="s" s="0">
+        <ns0:v>81</ns0:v>
+      </ns0:c>
+      <ns0:c r="B59" t="s" s="0">
+        <ns0:v>98</ns0:v>
+      </ns0:c>
+      <ns0:c r="C59" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D59" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E59" t="s" s="0">
+        <ns0:v>179</ns0:v>
+      </ns0:c>
+      <ns0:c r="F59" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G59" t="s" s="0">
+        <ns0:v>90</ns0:v>
+      </ns0:c>
+      <ns0:c r="H59" t="s" s="0">
+        <ns0:v>207</ns0:v>
+      </ns0:c>
+      <ns0:c r="I59" t="s" s="0">
+        <ns0:v>208</ns0:v>
       </ns0:c>
     </ns0:row>
   </ns0:sheetData>
@@ -3921,7 +5408,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:dimension ref="A1:AI40"/>
+  <ns0:dimension ref="A1:AL43"/>
   <ns0:sheetData>
     <ns0:row r="1">
       <ns0:c r="A1" t="s" s="0">
@@ -4029,6 +5516,15 @@
       <ns0:c r="AI1" t="s" s="0">
         <ns0:v>155</ns0:v>
       </ns0:c>
+      <ns0:c r="AJ1" t="s" s="0">
+        <ns0:v>186</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK1" t="s" s="0">
+        <ns0:v>187</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL1" t="s" s="0">
+        <ns0:v>188</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="2">
       <ns0:c r="A2" t="s" s="0">
@@ -4136,13 +5632,22 @@
       <ns0:c r="AI2" t="s" s="0">
         <ns0:v>31</ns0:v>
       </ns0:c>
+      <ns0:c r="AJ2" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK2" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL2" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="3">
       <ns0:c r="A3" t="s" s="0">
         <ns0:v>162</ns0:v>
       </ns0:c>
       <ns0:c r="B3" t="s" s="0">
-        <ns0:v>109</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
       <ns0:c r="C3" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -4154,25 +5659,25 @@
         <ns0:v>109</ns0:v>
       </ns0:c>
       <ns0:c r="F3" t="s" s="0">
-        <ns0:v>109</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
       <ns0:c r="G3" t="s" s="0">
-        <ns0:v>109</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
       <ns0:c r="H3" t="s" s="0">
-        <ns0:v>109</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
       <ns0:c r="I3" t="s" s="0">
         <ns0:v>11</ns0:v>
       </ns0:c>
       <ns0:c r="J3" t="s" s="0">
-        <ns0:v>109</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
       <ns0:c r="K3" t="s" s="0">
         <ns0:v>109</ns0:v>
       </ns0:c>
       <ns0:c r="L3" t="s" s="0">
-        <ns0:v>109</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
       <ns0:c r="M3" t="s" s="0">
         <ns0:v>109</ns0:v>
@@ -4193,7 +5698,7 @@
         <ns0:v>109</ns0:v>
       </ns0:c>
       <ns0:c r="S3" t="s" s="0">
-        <ns0:v>109</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
       <ns0:c r="T3" t="s" s="0">
         <ns0:v>109</ns0:v>
@@ -4202,7 +5707,7 @@
         <ns0:v>109</ns0:v>
       </ns0:c>
       <ns0:c r="V3" t="s" s="0">
-        <ns0:v>109</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
       <ns0:c r="W3" t="s" s="0">
         <ns0:v>109</ns0:v>
@@ -4217,30 +5722,39 @@
         <ns0:v>109</ns0:v>
       </ns0:c>
       <ns0:c r="AA3" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="AB3" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="AC3" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="AD3" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE3" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF3" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG3" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH3" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="AI3" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ3" t="s" s="0">
         <ns0:v>109</ns0:v>
       </ns0:c>
-      <ns0:c r="AB3" t="s" s="0">
+      <ns0:c r="AK3" t="s" s="0">
         <ns0:v>109</ns0:v>
       </ns0:c>
-      <ns0:c r="AC3" t="s" s="0">
-        <ns0:v>109</ns0:v>
-      </ns0:c>
-      <ns0:c r="AD3" t="s" s="0">
-        <ns0:v>109</ns0:v>
-      </ns0:c>
-      <ns0:c r="AE3" t="s" s="0">
-        <ns0:v>109</ns0:v>
-      </ns0:c>
-      <ns0:c r="AF3" t="s" s="0">
-        <ns0:v>109</ns0:v>
-      </ns0:c>
-      <ns0:c r="AG3" t="s" s="0">
-        <ns0:v>109</ns0:v>
-      </ns0:c>
-      <ns0:c r="AH3" t="s" s="0">
-        <ns0:v>109</ns0:v>
-      </ns0:c>
-      <ns0:c r="AI3" t="s" s="0">
+      <ns0:c r="AL3" t="s" s="0">
         <ns0:v>109</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -4260,10 +5774,10 @@
         <ns0:v>122</ns0:v>
       </ns0:c>
       <ns0:c r="B7" t="s" s="0">
-        <ns0:v>172</ns0:v>
+        <ns0:v>208</ns0:v>
       </ns0:c>
       <ns0:c r="C7" t="s" s="0">
-        <ns0:v>18</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="8">
@@ -4304,10 +5818,10 @@
         <ns0:v>126</ns0:v>
       </ns0:c>
       <ns0:c r="B11" t="s" s="0">
-        <ns0:v>173</ns0:v>
+        <ns0:v>211</ns0:v>
       </ns0:c>
       <ns0:c r="C11" t="s" s="0">
-        <ns0:v>28</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="12">
@@ -4315,10 +5829,10 @@
         <ns0:v>127</ns0:v>
       </ns0:c>
       <ns0:c r="B12" t="s" s="0">
-        <ns0:v>173</ns0:v>
+        <ns0:v>211</ns0:v>
       </ns0:c>
       <ns0:c r="C12" t="s" s="0">
-        <ns0:v>25</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="13">
@@ -4326,10 +5840,10 @@
         <ns0:v>128</ns0:v>
       </ns0:c>
       <ns0:c r="B13" t="s" s="0">
-        <ns0:v>172</ns0:v>
+        <ns0:v>208</ns0:v>
       </ns0:c>
       <ns0:c r="C13" t="s" s="0">
-        <ns0:v>31</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="14">
@@ -4348,10 +5862,10 @@
         <ns0:v>130</ns0:v>
       </ns0:c>
       <ns0:c r="B15" t="s" s="0">
-        <ns0:v>173</ns0:v>
+        <ns0:v>211</ns0:v>
       </ns0:c>
       <ns0:c r="C15" t="s" s="0">
-        <ns0:v>25</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="16">
@@ -4370,10 +5884,10 @@
         <ns0:v>132</ns0:v>
       </ns0:c>
       <ns0:c r="B17" t="s" s="0">
-        <ns0:v>173</ns0:v>
+        <ns0:v>211</ns0:v>
       </ns0:c>
       <ns0:c r="C17" t="s" s="0">
-        <ns0:v>28</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="18">
@@ -4447,10 +5961,10 @@
         <ns0:v>139</ns0:v>
       </ns0:c>
       <ns0:c r="B24" t="s" s="0">
-        <ns0:v>174</ns0:v>
+        <ns0:v>218</ns0:v>
       </ns0:c>
       <ns0:c r="C24" t="s" s="0">
-        <ns0:v>54</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="25">
@@ -4480,10 +5994,10 @@
         <ns0:v>142</ns0:v>
       </ns0:c>
       <ns0:c r="B27" t="s" s="0">
-        <ns0:v>172</ns0:v>
+        <ns0:v>208</ns0:v>
       </ns0:c>
       <ns0:c r="C27" t="s" s="0">
-        <ns0:v>18</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="28">
@@ -4535,10 +6049,10 @@
         <ns0:v>147</ns0:v>
       </ns0:c>
       <ns0:c r="B32" t="s" s="0">
-        <ns0:v>175</ns0:v>
+        <ns0:v>167</ns0:v>
       </ns0:c>
       <ns0:c r="C32" t="s" s="0">
-        <ns0:v>69</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="33">
@@ -4546,10 +6060,10 @@
         <ns0:v>148</ns0:v>
       </ns0:c>
       <ns0:c r="B33" t="s" s="0">
-        <ns0:v>172</ns0:v>
+        <ns0:v>208</ns0:v>
       </ns0:c>
       <ns0:c r="C33" t="s" s="0">
-        <ns0:v>18</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="34">
@@ -4557,10 +6071,10 @@
         <ns0:v>149</ns0:v>
       </ns0:c>
       <ns0:c r="B34" t="s" s="0">
-        <ns0:v>174</ns0:v>
+        <ns0:v>218</ns0:v>
       </ns0:c>
       <ns0:c r="C34" t="s" s="0">
-        <ns0:v>54</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="35">
@@ -4568,10 +6082,10 @@
         <ns0:v>150</ns0:v>
       </ns0:c>
       <ns0:c r="B35" t="s" s="0">
-        <ns0:v>172</ns0:v>
+        <ns0:v>208</ns0:v>
       </ns0:c>
       <ns0:c r="C35" t="s" s="0">
-        <ns0:v>31</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="36">
@@ -4579,10 +6093,10 @@
         <ns0:v>151</ns0:v>
       </ns0:c>
       <ns0:c r="B36" t="s" s="0">
-        <ns0:v>176</ns0:v>
+        <ns0:v>222</ns0:v>
       </ns0:c>
       <ns0:c r="C36" t="s" s="0">
-        <ns0:v>90</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="37">
@@ -4590,10 +6104,10 @@
         <ns0:v>152</ns0:v>
       </ns0:c>
       <ns0:c r="B37" t="s" s="0">
-        <ns0:v>172</ns0:v>
+        <ns0:v>208</ns0:v>
       </ns0:c>
       <ns0:c r="C37" t="s" s="0">
-        <ns0:v>18</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="38">
@@ -4601,10 +6115,10 @@
         <ns0:v>153</ns0:v>
       </ns0:c>
       <ns0:c r="B38" t="s" s="0">
-        <ns0:v>172</ns0:v>
+        <ns0:v>208</ns0:v>
       </ns0:c>
       <ns0:c r="C38" t="s" s="0">
-        <ns0:v>18</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="39">
@@ -4612,10 +6126,10 @@
         <ns0:v>154</ns0:v>
       </ns0:c>
       <ns0:c r="B39" t="s" s="0">
-        <ns0:v>173</ns0:v>
+        <ns0:v>211</ns0:v>
       </ns0:c>
       <ns0:c r="C39" t="s" s="0">
-        <ns0:v>25</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="40">
@@ -4623,10 +6137,43 @@
         <ns0:v>155</ns0:v>
       </ns0:c>
       <ns0:c r="B40" t="s" s="0">
-        <ns0:v>172</ns0:v>
+        <ns0:v>208</ns0:v>
       </ns0:c>
       <ns0:c r="C40" t="s" s="0">
-        <ns0:v>31</ns0:v>
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="41">
+      <ns0:c r="A41" t="s" s="0">
+        <ns0:v>186</ns0:v>
+      </ns0:c>
+      <ns0:c r="B41" t="s" s="0">
+        <ns0:v>164</ns0:v>
+      </ns0:c>
+      <ns0:c r="C41" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="42">
+      <ns0:c r="A42" t="s" s="0">
+        <ns0:v>187</ns0:v>
+      </ns0:c>
+      <ns0:c r="B42" t="s" s="0">
+        <ns0:v>164</ns0:v>
+      </ns0:c>
+      <ns0:c r="C42" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="43">
+      <ns0:c r="A43" t="s" s="0">
+        <ns0:v>188</ns0:v>
+      </ns0:c>
+      <ns0:c r="B43" t="s" s="0">
+        <ns0:v>164</ns0:v>
+      </ns0:c>
+      <ns0:c r="C43" t="s" s="0">
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
   </ns0:sheetData>
